--- a/skiltracker-main.xlsx
+++ b/skiltracker-main.xlsx
@@ -1,158 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\SkilTracker\SkilTracker\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93EEE9C0-30A4-4BE4-B24D-53D24CFB2F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="2850" yWindow="2490" windowWidth="21600" windowHeight="11610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2850" yWindow="2490" windowWidth="21600" windowHeight="11610" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ID" sheetId="1" r:id="rId1"/>
-    <sheet name="Skills" sheetId="2" r:id="rId2"/>
+    <sheet name="ID" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Skills" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ID!$A$1:$E$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ID'!$A$1:$E$30</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="35">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Band</t>
-  </si>
-  <si>
-    <t>Sector</t>
-  </si>
-  <si>
-    <t>Dutch</t>
-  </si>
-  <si>
-    <t>Van der Linde</t>
-  </si>
-  <si>
-    <t>Cat1a</t>
-  </si>
-  <si>
-    <t>Cat1b</t>
-  </si>
-  <si>
-    <t>Cat2a</t>
-  </si>
-  <si>
-    <t>Cat2b</t>
-  </si>
-  <si>
-    <t>Cat2c</t>
-  </si>
-  <si>
-    <t>Cat2d</t>
-  </si>
-  <si>
-    <t>Cat2e</t>
-  </si>
-  <si>
-    <t>Cat3a</t>
-  </si>
-  <si>
-    <t>Cat3b</t>
-  </si>
-  <si>
-    <t>Cat3c</t>
-  </si>
-  <si>
-    <t>Cat3d</t>
-  </si>
-  <si>
-    <t>Cat3e</t>
-  </si>
-  <si>
-    <t>Planning</t>
-  </si>
-  <si>
-    <t>Leadership</t>
-  </si>
-  <si>
-    <t>Hosea</t>
-  </si>
-  <si>
-    <t>Matthews</t>
-  </si>
-  <si>
-    <t>RDR001</t>
-  </si>
-  <si>
-    <t>RDR002</t>
-  </si>
-  <si>
-    <t>Gunslinging</t>
-  </si>
-  <si>
-    <t>Heists</t>
-  </si>
-  <si>
-    <t>Fashion</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>Diplomacy</t>
-  </si>
-  <si>
-    <t>Warfare</t>
-  </si>
-  <si>
-    <t>History</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Teaching</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -171,21 +49,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -505,169 +442,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
-    <col min="2" max="2" width="20.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col width="20.375" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="20.375" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Last Name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Band</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RDR001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dutch</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Van der Linde</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
-        <v>20</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3">
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RDR002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Hosea</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Matthews</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>9</v>
       </c>
-      <c r="E3" t="s">
-        <v>20</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Leadership</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E30" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E2">
+  <autoFilter ref="A1:E30">
+    <sortState ref="A2:E2">
       <sortCondition ref="D1:D30"/>
     </sortState>
   </autoFilter>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" t="s">
-        <v>17</v>
-      </c>
-      <c r="M1" t="s">
-        <v>18</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Cat1a</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Cat1b</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Cat2a</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Cat2b</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Cat2c</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Cat2d</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Cat2e</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Cat3a</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Cat3b</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Cat3c</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Cat3d</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Cat3e</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RDR001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gunslinging</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Heists</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Fashion</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Warfare</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>History</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Diplomacy</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>34</v>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RDR002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Gunslinging</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Planning</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Capacity</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Reading</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Teaching</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/skiltracker-main.xlsx
+++ b/skiltracker-main.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col width="20.375" bestFit="1" customWidth="1" min="2" max="2"/>
@@ -528,6 +528,81 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>Leadership</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RDR003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Arthur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Morgan</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RDR004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>John</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Marston</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Enforcement</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RDR005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Roberts</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Support</t>
         </is>
       </c>
     </row>
@@ -547,7 +622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11" defaultRowHeight="15.75"/>
   <sheetData>
     <row r="1">
@@ -695,6 +770,123 @@
           <t>Teaching</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RDR003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Gunslinging</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Main Character</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Horseback Riding</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Native Affairs</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Foraging</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Horse Care</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Childcare</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RDR004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Main Character</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gunslinging</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Horseback Riding</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Family</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Hunting</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Foraging</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Gang Warfare</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RDR005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Motherhood</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/skiltracker-main.xlsx
+++ b/skiltracker-main.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\Documents\SkilTracker\SkilTracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631396B4-2753-4628-B84B-F645D85DEDB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CC9395C-8E6F-4D9B-ABCA-76FB987FE52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ID" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
   <si>
     <t>ID</t>
   </si>
@@ -65,87 +65,6 @@
     <t>Cat3e</t>
   </si>
   <si>
-    <t>RDR001</t>
-  </si>
-  <si>
-    <t>Planning</t>
-  </si>
-  <si>
-    <t>Gunslinging</t>
-  </si>
-  <si>
-    <t>Heists</t>
-  </si>
-  <si>
-    <t>Fashion</t>
-  </si>
-  <si>
-    <t>Warfare</t>
-  </si>
-  <si>
-    <t>History</t>
-  </si>
-  <si>
-    <t>Music</t>
-  </si>
-  <si>
-    <t>Diplomacy</t>
-  </si>
-  <si>
-    <t>RDR002</t>
-  </si>
-  <si>
-    <t>Capacity</t>
-  </si>
-  <si>
-    <t>Reading</t>
-  </si>
-  <si>
-    <t>Teaching</t>
-  </si>
-  <si>
-    <t>RDR003</t>
-  </si>
-  <si>
-    <t>Main Character</t>
-  </si>
-  <si>
-    <t>Horseback Riding</t>
-  </si>
-  <si>
-    <t>Native Affairs</t>
-  </si>
-  <si>
-    <t>Foraging</t>
-  </si>
-  <si>
-    <t>Hunting</t>
-  </si>
-  <si>
-    <t>Horse Care</t>
-  </si>
-  <si>
-    <t>Childcare</t>
-  </si>
-  <si>
-    <t>Management</t>
-  </si>
-  <si>
-    <t>RDR004</t>
-  </si>
-  <si>
-    <t>Family</t>
-  </si>
-  <si>
-    <t>Gang Warfare</t>
-  </si>
-  <si>
-    <t>RDR005</t>
-  </si>
-  <si>
-    <t>Motherhood</t>
-  </si>
-  <si>
     <t>Name</t>
   </si>
   <si>
@@ -156,48 +75,6 @@
   </si>
   <si>
     <t>Sector</t>
-  </si>
-  <si>
-    <t>Dutch</t>
-  </si>
-  <si>
-    <t>Van der Linde</t>
-  </si>
-  <si>
-    <t>Leadership</t>
-  </si>
-  <si>
-    <t>Hosea</t>
-  </si>
-  <si>
-    <t>Matthews</t>
-  </si>
-  <si>
-    <t>Arthur</t>
-  </si>
-  <si>
-    <t>Morgan</t>
-  </si>
-  <si>
-    <t>Enforcement</t>
-  </si>
-  <si>
-    <t>John</t>
-  </si>
-  <si>
-    <t>Marston</t>
-  </si>
-  <si>
-    <t>Abigail</t>
-  </si>
-  <si>
-    <t>Roberts</t>
-  </si>
-  <si>
-    <t>Support</t>
-  </si>
-  <si>
-    <t>Theft</t>
   </si>
 </sst>
 </file>
@@ -569,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="20.375" bestFit="1" customWidth="1"/>
@@ -581,101 +458,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="E1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D2">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D3">
-        <v>9</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D4">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D5">
-        <v>8</v>
-      </c>
-      <c r="E5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -690,7 +482,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -732,121 +524,6 @@
       </c>
       <c r="M1" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
